--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260817_tarde.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260817_tarde.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="958" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C627920-AEE1-495C-88D9-3E79E98964C8}"/>
+  <xr:revisionPtr revIDLastSave="967" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52DE728F-8823-45A8-A98A-2DB8F5852BBF}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="cbo" sheetId="2" r:id="rId2"/>
     <sheet name="bram" sheetId="3" r:id="rId3"/>
     <sheet name="starnav" sheetId="4" r:id="rId4"/>
+    <sheet name="oceanpact" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
   <si>
     <t>cbo</t>
   </si>
@@ -237,6 +238,9 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>ilha de santana</t>
   </si>
 </sst>
 </file>
@@ -1729,4 +1733,56 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF7ACA0-AD48-46B4-B354-9966CDC48538}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="6"/>
+      <c r="H2" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>